--- a/wico/数据表结构.xlsx
+++ b/wico/数据表结构.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23250" windowHeight="13170" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23250" windowHeight="13170" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="6" r:id="rId1"/>
@@ -18,14 +18,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'不良类型（上传，下载）'!$B$3:$E$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'零件清单（下载）'!$B$3:$K$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'座椅配置（下载）'!$C$3:$F$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'座椅配置（下载）'!$C$3:$F$866</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5622" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5670" uniqueCount="1286">
   <si>
     <t>SLIDE ADJR OUT L,FR SEAT</t>
   </si>
@@ -103,143 +103,143 @@
   </si>
   <si>
     <t>WICO</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4739132-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2VH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WicoPartNumber</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TsPartNumber</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PartName</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PartType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Importance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Supplier</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CarModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SeatModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RepairMethod</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂装刮花</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂油反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换端盖</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SLIDE ADJR OUT L,FR SEAT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Lot</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>INTEGER</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TEXT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Production Line</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>INTEGER</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NgInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sync</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>sqlite数据类型</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Mysql数据类型</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>VARCHAR</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DATE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DATETIME</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ManufactureDate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NgTime</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TINYINT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SMALLINT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>FC</t>
@@ -1419,7 +1419,7 @@
   </si>
   <si>
     <t>2QY</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1471,7 +1471,7 @@
   </si>
   <si>
     <t>2QY</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
@@ -1496,591 +1496,591 @@
   </si>
   <si>
     <t>手动-前排-右席座椅（NOR）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅（HEI）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅（NOR）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-414-210</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-后排-右席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-414-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-后排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-413-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-210</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-220</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-419-310</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-419-520</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-418-410</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">2311-418-720 </t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4739141-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4739162-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4739231-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4739242-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745521-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745421-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745511-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745411-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745212-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3745112-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3725542-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3725612-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3725522-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742412-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742411-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742431-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742421-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742441-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4729910-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4729920-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4831510-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4055340-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4597110-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4420420-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4638170-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4639710-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>184-040010-5-0010</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3466360-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4734620-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4735622-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3488270K-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4785410-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3390210W-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3390250-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-110-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-120-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-220-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-210-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3488270-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4734650-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-558-210</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-557-210</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-558-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4816230-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3390210W-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-566-610</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-566-520</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-565-510</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-565-420</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-110-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-120-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-220-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-210-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3488270-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-120-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-220-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-210-2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3488270-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4734650-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-589-610</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-588-610</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-589-520</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-588-520</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4586310-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-565-420</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-566-520</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-565-710</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-566-810</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-598-320</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-598-410</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-599-420</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-599-510</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-389-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-389-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-418-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-550-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-550-420</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-549-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-549-420</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4855440-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4855430-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742452-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742462-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742451-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3742461-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-3928350-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4922310-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4922410-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4638180-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-598-310</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>2311-599-410</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>2311-599-520</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>2311-550-410</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>2311-549-410</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>21-3466360-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3390250-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4420420-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3441510-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2VH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2VH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2LQ</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2LQ</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2HY</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2HY</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2WB</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2WB</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2UB</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2UB</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2VP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2VP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2FW</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3BS</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3BS</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2GN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2GN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YC</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YC</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-550-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-549-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-598-420</t>
-    <phoneticPr fontId="31"/>
+    <phoneticPr fontId="32"/>
   </si>
   <si>
     <t>23-4767052-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>21-3675720-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-中排-右席座椅</t>
@@ -2107,392 +2107,392 @@
   </si>
   <si>
     <t>23-4767052-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-前排-右席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-左席座椅（8WAY带记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-左席座椅（8WAY无记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-右席座椅（4WAY无记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-557-120</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-中排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-中排-右席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PartPicUrl</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑块</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>不在初始位</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整到初始位</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑动电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换H型滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>后升降震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节制动器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换制动器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂润滑油，反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>螺丝孔滑牙</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节丝杆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂油反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>齿轮箱支架装配孔滑牙</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换条码</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>上导轨螺丝脱落</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>锁紧挡圈松动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>敲紧挡圈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前/后端连接臂铆接过紧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前/后端连接臂铆接过松</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换侧支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>铜棒敲击修理</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>刮花部位涂油漆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降反转音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降电机不作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降打啃</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节到初始位</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CM_Date</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3QY</t>
   </si>
   <si>
     <t>3QY</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2LQ</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3LQ</t>
   </si>
   <si>
     <t>3LQ</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手柄变形</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>有凹坑</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涡卷弹簧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>生锈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>除锈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换涡卷弹簧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>植毛破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>扇形齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>绕性轴（短）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>有压痕</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换扇形齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>有裂纹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>冲压侧支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换冲压侧支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>漏冲孔</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>插头破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>插头内粘附焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>脉冲功能失效（按下按钮只能动一点）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电机声音过大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>锁紧挡圈欠品</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>装了2枚锁紧挡圈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>翻边轮廓不良</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>用工具掰正</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨前端解锁小支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>变位拉杆不回弹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>制动器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换制动器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>作动时有异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>作动很多次座椅才能升到顶端</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手柄回位不顺畅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>变位拉杆松动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>插头内粘附焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/153-080025-5.jpg</t>
@@ -3135,179 +3135,179 @@
   </si>
   <si>
     <t>涡卷弹簧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>上导轨螺丝滑牙</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2022-05-14</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2YT</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Day</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Night</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2022-05-14 15:35:51</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2022-05-13</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动缓慢</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降缓慢</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降反转音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>端盖破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换端盖</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DATE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2HY</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>23-4739242-2</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>2022-02-16</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2LQ</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>ComplainDate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CarModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WicoPartNumber</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PartName</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NgInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SLIDE ADJR INN L,FR SEAT（8WAY）</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>内侧滑轨铆钉漏铆接</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>2022-06-20</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">SLIDE ADJR INN L,FR SEAT（8WAY） </t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅在最前端滑不动</t>
-    <phoneticPr fontId="33" type="noConversion"/>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
   <si>
     <t>调角器电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>作动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电机声音过大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>弹簧松动/脱落</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换弹簧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>英国电动-前排-右席座椅（8WAY带记忆）</t>
@@ -3320,11 +3320,11 @@
   </si>
   <si>
     <t>后升降无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>清除焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>81201-3A02-X810-M1-0000</t>
@@ -3367,23 +3367,23 @@
   </si>
   <si>
     <t>滑轨无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑轨无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换H型滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>条码脏污/破损，无法识别</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-310</t>
@@ -3393,642 +3393,642 @@
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2110-355-310.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2110-355-320.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>58104/58112</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3B4A</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-后排-左席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动-后排-右席座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-310</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2110-355-320</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>L001779025</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>L001779035</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MINI RECLINER ASSY_RH，MANUAL</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MINI RECLINER ASSY_LH，MANUAL</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬L形支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动拉力过大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂润滑油，反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>轴弯曲了</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>绕性轴（短）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>绕性轴（长）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑轨震动并且晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电机破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PartType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RepairMethod</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降电机异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>变形</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Regular</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>([0-9]{2})([A-L])([0-3][0-9])([A-M]) ([0-9]{3})</t>
   </si>
   <si>
     <t>涂油反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整/更换 短绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整/更换 长绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>条码脏污/破损，无法识别</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降干涉异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动途中卡死，无法再前后作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动途中卡死，无法再前后作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动到最前/后端</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>作动到最前端后无法返回</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑块</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>敲护架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>上导轨螺丝滑牙</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>作动到最顶/底端时有死点音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃&amp;异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降缓慢</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂油反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动到最前/后端</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节滑动电机支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂油反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动到最前/后端</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动电机连接板破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换H型滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬扇形齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃&amp;异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>扣条异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑轨震动并且晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃&amp;异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>清理齿部的焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动打啃</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降电机异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>紧固电机螺丝</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>73M0([1-9A-E])1([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>73M0([1-9A-E])B([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>73M0([1-9A-E])0([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>73M0([1-9A-E])A([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑轨震动并且晃动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节制动器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬扇形齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>清理齿部的焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降电动支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>后升降电动支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降电动支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降电动支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SIDE BRKT INN COMP R,FR CUSH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SIDE BRKT OUT L SUB COMP,FR CUSH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>齿轮箱破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整/更换 短绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整/更换 长绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>涂润滑油，反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换丝杆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>后升降震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调角器电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电机破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整丝杆螺母，反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整丝杆螺母</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换座椅骨架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手柄上拉后不回弹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑动电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑动电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换前升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>后升降震动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>后升降异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换后升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前升降异音</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>不在初始位</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>与骨盆之间的间隙小</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换解锁手柄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-525-310</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DE5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4077,294 +4077,294 @@
       </rPr>
       <t>右席座椅</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DE5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>有划痕</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃&amp;异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动座椅</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动打啃</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬L形支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调整升降电机</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>连接管内有焊渣、焊瘤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>去除焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换侧支架</t>
   </si>
   <si>
     <t>连接管内有焊渣、焊瘤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换侧支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>紧固电机螺丝</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>锁紧挡圈脱落</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>插头破损</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TS-GSK漏装短轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>协助更换齿轮箱,调整/更换 短绕性轴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬解锁手柄进行修理</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>与骨盆之间的间隙小</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>调节连接板</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>手柄下压后不回弹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>取出焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑动途中卡死，无法再前后作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换齿轮箱</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换丝杆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动到最前/后端</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>撬L形支架</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换丝杆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降异响</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>二维码破损/脏污</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>清理焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无法作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>清理焊渣</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>重新装配</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>前/后端连接臂铆接过紧</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>座椅不同步</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>重新装配</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>滑轨无法锁止</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换滑轨</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更改变位拉杆</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>英国电动-前排-右席座椅（8WAY带记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>英国电动-前排-左席座椅（4WAY无记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4855440-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>23-4855430-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁力大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>急速作动靠背时飞齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>内阻大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Custom</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TS-GSK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>LEAR</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CarModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SeatModel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WicoPartNumber</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>反复作动</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>更换调角器</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>报废</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>二维码无法识别</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>解锁力大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>急速作动靠背时飞齿</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>内阻大</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>报废</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>磨电机安装孔</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>升降打啃</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-627-110</t>
@@ -4383,106 +4383,106 @@
   </si>
   <si>
     <t>DB2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-599-520.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-627-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-627-110.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-628-110</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-628-110.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1627([1-9A-E])0([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1628([1-9A-E])0([1-9A-C])([1-9A-HJ-NP-X])([0-9A-F]{3})([0-9A-Z])([WT])</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3EA</t>
   </si>
   <si>
     <t>3EA</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TS-GSK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-左席座椅（8WAY带记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-左席座椅（8WAY带记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-右席座椅（4WAY无记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>电动-前排-右席座椅（4WAY无记忆）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-549-620</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-550-620</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>81536-33W5-H000-TA-0000</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>81536-33W5-H000-TB-0000</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>([0-9]{2})([A-L])([0-3][0-9])([A-M]) ([0-9]{3})</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>([0-9]{2})([A-L])([0-3][0-9])([A-M]) ([0-9]{3})</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-549-620</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-549-620.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2311-550-620</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-550-620.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TS-GSK</t>
@@ -4492,26 +4492,130 @@
   </si>
   <si>
     <t>3YA</t>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-550-520.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-549-520.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-549-520</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>81536-3M14-SE00-TA-0000</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-550-520</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-550-620</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-549-520</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-549-620</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-550-510</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-550-610</t>
+  </si>
+  <si>
+    <t>2311-550-610</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-549-510</t>
+  </si>
+  <si>
+    <t>2311-549-510</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-549-610</t>
+  </si>
+  <si>
+    <t>2311-549-610</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>81136-3M14-S700-TB-0000</t>
+  </si>
+  <si>
+    <t>81136-3E76-E800-TB-0000</t>
+  </si>
+  <si>
+    <t>81136-3M14-S700-TA-0000</t>
+  </si>
+  <si>
+    <t>81136-3E76-E800-TA-0000</t>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-550-510.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-550-610.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-549-510.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-549-610.jpg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2311-550-520</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>81536-3M14-SE00-TB-0000</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>后升降电动支架</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4916,32 +5020,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="513">
+  <cellStyleXfs count="537">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
@@ -4980,496 +5120,485 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5479,36 +5608,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5524,7 +5644,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5556,6 +5691,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5565,6 +5702,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5587,8 +5725,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5598,7 +5738,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5621,10 +5760,198 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5690,175 +6017,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5882,25 +6052,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5909,7 +6079,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5921,16 +6091,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5939,10 +6109,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="377" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="377" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5951,7 +6121,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5960,7 +6130,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5969,42 +6139,44 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="1" xfId="269" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="1" xfId="269" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="377" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="377" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="383" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="383" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="383" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="383" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="300" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="310" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="452" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="452" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="383" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="383" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="377" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="513">
+  <cellStyles count="537">
     <cellStyle name="_x0004_" xfId="2"/>
     <cellStyle name="_x0004_ 2" xfId="3"/>
     <cellStyle name="_1月" xfId="4"/>
@@ -6277,10 +6449,12 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 10" xfId="269"/>
     <cellStyle name="常规 10 2" xfId="383"/>
+    <cellStyle name="常规 10 2 2" xfId="536"/>
     <cellStyle name="常规 10 3" xfId="452"/>
     <cellStyle name="常规 11" xfId="270"/>
     <cellStyle name="常规 11 2" xfId="382"/>
     <cellStyle name="常规 11 2 2" xfId="445"/>
+    <cellStyle name="常规 11 2 3" xfId="530"/>
     <cellStyle name="常规 11 3" xfId="395"/>
     <cellStyle name="常规 11 3 2" xfId="484"/>
     <cellStyle name="常规 11 4" xfId="406"/>
@@ -6289,6 +6463,7 @@
     <cellStyle name="常规 11 5 2" xfId="507"/>
     <cellStyle name="常规 11 6" xfId="453"/>
     <cellStyle name="常规 11 7" xfId="433"/>
+    <cellStyle name="常规 11 8" xfId="518"/>
     <cellStyle name="常规 12" xfId="271"/>
     <cellStyle name="常规 12 2" xfId="412"/>
     <cellStyle name="常规 12 3" xfId="454"/>
@@ -6298,6 +6473,7 @@
     <cellStyle name="常规 14" xfId="1"/>
     <cellStyle name="常规 14 2" xfId="451"/>
     <cellStyle name="常规 14 3" xfId="439"/>
+    <cellStyle name="常规 14 4" xfId="524"/>
     <cellStyle name="常规 15" xfId="375"/>
     <cellStyle name="常规 15 2" xfId="472"/>
     <cellStyle name="常规 15 3" xfId="427"/>
@@ -6326,13 +6502,16 @@
     <cellStyle name="常规 3" xfId="283"/>
     <cellStyle name="常规 3 10" xfId="459"/>
     <cellStyle name="常规 3 11" xfId="428"/>
+    <cellStyle name="常规 3 12" xfId="513"/>
     <cellStyle name="常规 3 2" xfId="284"/>
     <cellStyle name="常规 3 2 2" xfId="285"/>
     <cellStyle name="常规 3 2 2 2" xfId="286"/>
     <cellStyle name="常规 3 3" xfId="287"/>
+    <cellStyle name="常规 3 3 10" xfId="516"/>
     <cellStyle name="常规 3 3 2" xfId="288"/>
     <cellStyle name="常规 3 3 2 2" xfId="387"/>
     <cellStyle name="常规 3 3 2 2 2" xfId="449"/>
+    <cellStyle name="常规 3 3 2 2 3" xfId="534"/>
     <cellStyle name="常规 3 3 2 3" xfId="399"/>
     <cellStyle name="常规 3 3 2 3 2" xfId="488"/>
     <cellStyle name="常规 3 3 2 4" xfId="410"/>
@@ -6341,8 +6520,10 @@
     <cellStyle name="常规 3 3 2 5 2" xfId="511"/>
     <cellStyle name="常规 3 3 2 6" xfId="461"/>
     <cellStyle name="常规 3 3 2 7" xfId="437"/>
+    <cellStyle name="常规 3 3 2 8" xfId="522"/>
     <cellStyle name="常规 3 3 3" xfId="366"/>
     <cellStyle name="常规 3 3 3 2" xfId="443"/>
+    <cellStyle name="常规 3 3 3 3" xfId="528"/>
     <cellStyle name="常规 3 3 4" xfId="380"/>
     <cellStyle name="常规 3 3 4 2" xfId="476"/>
     <cellStyle name="常规 3 3 5" xfId="393"/>
@@ -6356,6 +6537,7 @@
     <cellStyle name="常规 3 4" xfId="289"/>
     <cellStyle name="常规 3 4 2" xfId="384"/>
     <cellStyle name="常规 3 4 2 2" xfId="446"/>
+    <cellStyle name="常规 3 4 2 3" xfId="531"/>
     <cellStyle name="常规 3 4 3" xfId="396"/>
     <cellStyle name="常规 3 4 3 2" xfId="485"/>
     <cellStyle name="常规 3 4 4" xfId="407"/>
@@ -6364,8 +6546,10 @@
     <cellStyle name="常规 3 4 5 2" xfId="508"/>
     <cellStyle name="常规 3 4 6" xfId="462"/>
     <cellStyle name="常规 3 4 7" xfId="434"/>
+    <cellStyle name="常规 3 4 8" xfId="519"/>
     <cellStyle name="常规 3 5" xfId="374"/>
     <cellStyle name="常规 3 5 2" xfId="440"/>
+    <cellStyle name="常规 3 5 3" xfId="525"/>
     <cellStyle name="常规 3 6" xfId="376"/>
     <cellStyle name="常规 3 6 2" xfId="473"/>
     <cellStyle name="常规 3 7" xfId="390"/>
@@ -6376,10 +6560,13 @@
     <cellStyle name="常规 3 9 2" xfId="502"/>
     <cellStyle name="常规 4" xfId="290"/>
     <cellStyle name="常规 4 10" xfId="429"/>
+    <cellStyle name="常规 4 11" xfId="514"/>
     <cellStyle name="常规 4 2" xfId="291"/>
+    <cellStyle name="常规 4 2 10" xfId="517"/>
     <cellStyle name="常规 4 2 2" xfId="292"/>
     <cellStyle name="常规 4 2 2 2" xfId="388"/>
     <cellStyle name="常规 4 2 2 2 2" xfId="450"/>
+    <cellStyle name="常规 4 2 2 2 3" xfId="535"/>
     <cellStyle name="常规 4 2 2 3" xfId="400"/>
     <cellStyle name="常规 4 2 2 3 2" xfId="489"/>
     <cellStyle name="常规 4 2 2 4" xfId="411"/>
@@ -6388,8 +6575,10 @@
     <cellStyle name="常规 4 2 2 5 2" xfId="512"/>
     <cellStyle name="常规 4 2 2 6" xfId="465"/>
     <cellStyle name="常规 4 2 2 7" xfId="438"/>
+    <cellStyle name="常规 4 2 2 8" xfId="523"/>
     <cellStyle name="常规 4 2 3" xfId="365"/>
     <cellStyle name="常规 4 2 3 2" xfId="444"/>
+    <cellStyle name="常规 4 2 3 3" xfId="529"/>
     <cellStyle name="常规 4 2 4" xfId="381"/>
     <cellStyle name="常规 4 2 4 2" xfId="477"/>
     <cellStyle name="常规 4 2 5" xfId="394"/>
@@ -6403,6 +6592,7 @@
     <cellStyle name="常规 4 3" xfId="293"/>
     <cellStyle name="常规 4 3 2" xfId="385"/>
     <cellStyle name="常规 4 3 2 2" xfId="447"/>
+    <cellStyle name="常规 4 3 2 3" xfId="532"/>
     <cellStyle name="常规 4 3 3" xfId="397"/>
     <cellStyle name="常规 4 3 3 2" xfId="486"/>
     <cellStyle name="常规 4 3 4" xfId="408"/>
@@ -6411,8 +6601,10 @@
     <cellStyle name="常规 4 3 5 2" xfId="509"/>
     <cellStyle name="常规 4 3 6" xfId="466"/>
     <cellStyle name="常规 4 3 7" xfId="435"/>
+    <cellStyle name="常规 4 3 8" xfId="520"/>
     <cellStyle name="常规 4 4" xfId="370"/>
     <cellStyle name="常规 4 4 2" xfId="441"/>
+    <cellStyle name="常规 4 4 3" xfId="526"/>
     <cellStyle name="常规 4 5" xfId="378"/>
     <cellStyle name="常规 4 5 2" xfId="474"/>
     <cellStyle name="常规 4 6" xfId="391"/>
@@ -6427,9 +6619,11 @@
     <cellStyle name="常规 5 2 2" xfId="296"/>
     <cellStyle name="常规 5 3" xfId="297"/>
     <cellStyle name="常规 6" xfId="298"/>
+    <cellStyle name="常规 6 10" xfId="515"/>
     <cellStyle name="常规 6 2" xfId="299"/>
     <cellStyle name="常规 6 2 2" xfId="386"/>
     <cellStyle name="常规 6 2 2 2" xfId="448"/>
+    <cellStyle name="常规 6 2 2 3" xfId="533"/>
     <cellStyle name="常规 6 2 3" xfId="398"/>
     <cellStyle name="常规 6 2 3 2" xfId="487"/>
     <cellStyle name="常规 6 2 4" xfId="409"/>
@@ -6438,8 +6632,10 @@
     <cellStyle name="常规 6 2 5 2" xfId="510"/>
     <cellStyle name="常规 6 2 6" xfId="468"/>
     <cellStyle name="常规 6 2 7" xfId="436"/>
+    <cellStyle name="常规 6 2 8" xfId="521"/>
     <cellStyle name="常规 6 3" xfId="367"/>
     <cellStyle name="常规 6 3 2" xfId="442"/>
+    <cellStyle name="常规 6 3 3" xfId="527"/>
     <cellStyle name="常规 6 4" xfId="379"/>
     <cellStyle name="常规 6 4 2" xfId="475"/>
     <cellStyle name="常规 6 5" xfId="392"/>
@@ -6549,7 +6745,7 @@
         <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6610,7 +6806,7 @@
         <xdr:cNvPr id="3" name="图片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6671,7 +6867,7 @@
         <xdr:cNvPr id="5" name="图片 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6727,7 +6923,7 @@
         <xdr:cNvPr id="7" name="TextBox 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6785,7 +6981,7 @@
         <xdr:cNvPr id="8" name="TextBox 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6843,7 +7039,7 @@
         <xdr:cNvPr id="13" name="TextBox 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6906,7 +7102,7 @@
         <xdr:cNvPr id="16" name="直接箭头连接符 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6959,7 +7155,7 @@
         <xdr:cNvPr id="21" name="图片 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000015000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7020,7 +7216,7 @@
         <xdr:cNvPr id="23" name="图片 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000017000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7081,7 +7277,7 @@
         <xdr:cNvPr id="24" name="直接箭头连接符 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7134,7 +7330,7 @@
         <xdr:cNvPr id="27" name="直接箭头连接符 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7187,7 +7383,7 @@
         <xdr:cNvPr id="29" name="直接箭头连接符 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00001D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7240,7 +7436,7 @@
         <xdr:cNvPr id="31" name="直接箭头连接符 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00001F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7293,7 +7489,7 @@
         <xdr:cNvPr id="33" name="直接箭头连接符 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000021000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7346,7 +7542,7 @@
         <xdr:cNvPr id="36" name="直接箭头连接符 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000024000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7394,7 +7590,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7781,7 +7977,7 @@
       <c r="T32" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7792,7 +7988,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -13038,9 +13234,201 @@
         <v>0</v>
       </c>
     </row>
+    <row r="159" spans="2:12">
+      <c r="B159" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F159" s="53" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I159" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J159" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K159" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12">
+      <c r="B160" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F160" s="53" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I160" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J160" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K160" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11">
+      <c r="B161" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F161" s="53" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I161" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J161" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K161" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11">
+      <c r="B162" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F162" s="53" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I162" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J162" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K162" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11">
+      <c r="B163" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F163" s="53" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I163" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J163" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K163" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11">
+      <c r="B164" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F164" s="53" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I164" s="9">
+        <v>58109</v>
+      </c>
+      <c r="J164" s="54" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K164" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B3:K154"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F153" r:id="rId1"/>
     <hyperlink ref="F154" r:id="rId2"/>
@@ -13050,9 +13438,17 @@
     <hyperlink ref="F157:F158" r:id="rId6" display="http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-628-110.jpg"/>
     <hyperlink ref="F157" r:id="rId7"/>
     <hyperlink ref="F158" r:id="rId8"/>
+    <hyperlink ref="F159:F160" r:id="rId9" display="http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-628-110.jpg"/>
+    <hyperlink ref="F159" r:id="rId10"/>
+    <hyperlink ref="F160" r:id="rId11"/>
+    <hyperlink ref="F161:F164" r:id="rId12" display="http://gitee.com/sunny_ho/image_bed/raw/master/wico/2311-628-110.jpg"/>
+    <hyperlink ref="F161" r:id="rId13"/>
+    <hyperlink ref="F162" r:id="rId14"/>
+    <hyperlink ref="F163" r:id="rId15"/>
+    <hyperlink ref="F164" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="22" orientation="landscape" r:id="rId9"/>
+  <pageSetup paperSize="9" scale="22" orientation="landscape" r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -25462,7 +25858,7 @@
         <v>611</v>
       </c>
       <c r="E728" s="50" t="s">
-        <v>225</v>
+        <v>1265</v>
       </c>
       <c r="F728" s="48">
         <v>0</v>
@@ -25479,7 +25875,7 @@
         <v>611</v>
       </c>
       <c r="E729" s="50" t="s">
-        <v>222</v>
+        <v>1267</v>
       </c>
       <c r="F729" s="48">
         <v>0</v>
@@ -25700,7 +26096,7 @@
         <v>457</v>
       </c>
       <c r="E742" s="50" t="s">
-        <v>223</v>
+        <v>1264</v>
       </c>
       <c r="F742" s="48">
         <v>0</v>
@@ -25717,7 +26113,7 @@
         <v>457</v>
       </c>
       <c r="E743" s="50" t="s">
-        <v>220</v>
+        <v>1266</v>
       </c>
       <c r="F743" s="48">
         <v>0</v>
@@ -26227,7 +26623,7 @@
         <v>968</v>
       </c>
       <c r="E773" s="50" t="s">
-        <v>389</v>
+        <v>1270</v>
       </c>
       <c r="F773" s="52">
         <v>0</v>
@@ -26244,7 +26640,7 @@
         <v>968</v>
       </c>
       <c r="E774" s="50" t="s">
-        <v>386</v>
+        <v>1274</v>
       </c>
       <c r="F774" s="52">
         <v>0</v>
@@ -26465,7 +26861,7 @@
         <v>969</v>
       </c>
       <c r="E787" s="50" t="s">
-        <v>387</v>
+        <v>1268</v>
       </c>
       <c r="F787" s="52">
         <v>0</v>
@@ -26482,7 +26878,7 @@
         <v>969</v>
       </c>
       <c r="E788" s="50" t="s">
-        <v>384</v>
+        <v>1272</v>
       </c>
       <c r="F788" s="52">
         <v>0</v>
@@ -27179,7 +27575,7 @@
         <v>611</v>
       </c>
       <c r="E829" s="50" t="s">
-        <v>225</v>
+        <v>1265</v>
       </c>
       <c r="F829" s="48">
         <v>0</v>
@@ -27196,7 +27592,7 @@
         <v>611</v>
       </c>
       <c r="E830" s="50" t="s">
-        <v>222</v>
+        <v>1267</v>
       </c>
       <c r="F830" s="48">
         <v>0</v>
@@ -27417,7 +27813,7 @@
         <v>457</v>
       </c>
       <c r="E843" s="50" t="s">
-        <v>223</v>
+        <v>1264</v>
       </c>
       <c r="F843" s="48">
         <v>0</v>
@@ -27434,7 +27830,7 @@
         <v>457</v>
       </c>
       <c r="E844" s="50" t="s">
-        <v>220</v>
+        <v>1266</v>
       </c>
       <c r="F844" s="48">
         <v>0</v>
@@ -27815,8 +28211,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C3:F679"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <autoFilter ref="C3:F866"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -30964,7 +31360,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B3:E222"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31089,7 +31485,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -31447,7 +31843,7 @@
       <c r="P12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31533,7 +31929,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>